--- a/HoangThiHoai_Shopping/DataTest.xlsx
+++ b/HoangThiHoai_Shopping/DataTest.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
+    <sheet name="CheckoutInfo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>ER</t>
   </si>
@@ -52,6 +53,42 @@
   </si>
   <si>
     <t>emptyPass</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>ZipCode</t>
+  </si>
+  <si>
+    <t>ExpectedResult</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Doe</t>
+  </si>
+  <si>
+    <t>12345</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>error_first_name</t>
+  </si>
+  <si>
+    <t>error_last_name</t>
+  </si>
+  <si>
+    <t>error_zip_code</t>
   </si>
 </sst>
 </file>
@@ -441,4 +478,90 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/HoangThiHoai_Shopping/DataTest.xlsx
+++ b/HoangThiHoai_Shopping/DataTest.xlsx
@@ -4,11 +4,10 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
-    <sheet name="CheckoutInfo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>ER</t>
   </si>
@@ -53,42 +52,6 @@
   </si>
   <si>
     <t>emptyPass</t>
-  </si>
-  <si>
-    <t>FirstName</t>
-  </si>
-  <si>
-    <t>LastName</t>
-  </si>
-  <si>
-    <t>ZipCode</t>
-  </si>
-  <si>
-    <t>ExpectedResult</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Doe</t>
-  </si>
-  <si>
-    <t>12345</t>
-  </si>
-  <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>error_first_name</t>
-  </si>
-  <si>
-    <t>error_last_name</t>
-  </si>
-  <si>
-    <t>error_zip_code</t>
   </si>
 </sst>
 </file>
@@ -478,90 +441,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="17.5703125" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="25.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/HoangThiHoai_Shopping/DataTest.xlsx
+++ b/HoangThiHoai_Shopping/DataTest.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
+    <sheet name="CheckoutInfo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>ER</t>
   </si>
@@ -52,6 +53,42 @@
   </si>
   <si>
     <t>emptyPass</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>ZipCode</t>
+  </si>
+  <si>
+    <t>ExpectedResult</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Doe</t>
+  </si>
+  <si>
+    <t>12345</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>error_first_name</t>
+  </si>
+  <si>
+    <t>error_last_name</t>
+  </si>
+  <si>
+    <t>error_zip_code</t>
   </si>
 </sst>
 </file>
@@ -441,4 +478,90 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/HoangThiHoai_Shopping/DataTest.xlsx
+++ b/HoangThiHoai_Shopping/DataTest.xlsx
@@ -1,14 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_A5D66C1718FEA97C1D0919928E294C4DE9C377AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0660A424-F2AC-4543-922D-4AFB2B228D66}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
-    <sheet name="CheckoutInfo" sheetId="2" r:id="rId2"/>
+    <sheet name="E2E_Test" sheetId="3" r:id="rId2"/>
+    <sheet name="CheckoutInfo" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,10 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
-  <si>
-    <t>ER</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
   <si>
     <t>Username</t>
   </si>
@@ -89,12 +88,27 @@
   </si>
   <si>
     <t>error_zip_code</t>
+  </si>
+  <si>
+    <t>ProductName</t>
+  </si>
+  <si>
+    <t>Sauce Labs Backpack</t>
+  </si>
+  <si>
+    <t>E2E</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>99999</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -405,7 +419,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -416,62 +430,62 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -481,7 +495,57 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91516B9F-5D43-496B-863F-FCEABE4E557C}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -493,72 +557,72 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>13</v>
-      </c>
-      <c r="D1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
         <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/HoangThiHoai_Shopping/DataTest.xlsx
+++ b/HoangThiHoai_Shopping/DataTest.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_A5D66C1718FEA97C1D0919928E294C4DE9C377AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0660A424-F2AC-4543-922D-4AFB2B228D66}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_A5D66C1718FEA97C1D0919928E294C4DE9C377AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D09336E9-105E-4DDA-9F0C-541A7A932401}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
-    <sheet name="E2E_Test" sheetId="3" r:id="rId2"/>
+    <sheet name="EToE_Test" sheetId="3" r:id="rId2"/>
     <sheet name="CheckoutInfo" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -155,6 +155,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
